--- a/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:53:12+00:00</t>
+    <t>2026-08-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:08:45+00:00</t>
+    <t>2026-08-20T15:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:24:46+00:00</t>
+    <t>2026-08-21T08:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="86">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T08:13:05+00:00</t>
+    <t>2026-08-23T21:45:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -203,9 +203,6 @@
   </si>
   <si>
     <t>FRLMObservation.hasMember[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-ml-observation</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/R4/StructureDefinition/Observation</t>
@@ -802,7 +799,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -811,7 +808,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -819,7 +816,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -839,7 +836,7 @@
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -852,7 +849,7 @@
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -865,7 +862,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -891,7 +888,7 @@
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -904,7 +901,7 @@
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -930,7 +927,7 @@
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -943,7 +940,7 @@
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -956,7 +953,7 @@
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2"/>
     </row>
@@ -982,7 +979,7 @@
         <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -995,85 +992,85 @@
         <v>32</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E22" s="2"/>
     </row>

--- a/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="80">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-23T21:45:18+00:00</t>
+    <t>2026-08-24T13:13:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -166,7 +166,7 @@
     <t>FRLMObservation.order</t>
   </si>
   <si>
-    <t>Observation.inFulfillmentOf</t>
+    <t>Observation.sdtcInFulfillmentOf1</t>
   </si>
   <si>
     <t>FRLMObservation.bodySite</t>
@@ -208,9 +208,6 @@
     <t>http://hl7.org/fhir/R4/StructureDefinition/Observation</t>
   </si>
   <si>
-    <t>FRMLObservation</t>
-  </si>
-  <si>
     <t>Observation.status</t>
   </si>
   <si>
@@ -244,31 +241,16 @@
     <t>Observation.component</t>
   </si>
   <si>
-    <t>FRLMObservation.derivedFrom[FRLMObservation]</t>
-  </si>
-  <si>
     <t>Observation.derivedFrom:Observation</t>
   </si>
   <si>
-    <t>FRLMObservation.derivedFrom[FRLMLaboratoryObservation]</t>
-  </si>
-  <si>
     <t>Observation.derivedFrom:FRObservationLaboratoryReportResultsDocument</t>
   </si>
   <si>
-    <t>FRLMObservation.derivedFrom[FRLMImagingStudy]</t>
-  </si>
-  <si>
     <t>Observation.derivedFrom:FRImagingStudyDocument</t>
   </si>
   <si>
-    <t>FRLMObservation.hasMember[FRLMLaboratoryObservation]</t>
-  </si>
-  <si>
     <t>Observation.hasMember:FRObservationLaboratoryReportResultsDocument</t>
-  </si>
-  <si>
-    <t>FRLMObservation.hasMember[FRLMObservation]</t>
   </si>
   <si>
     <t>Observation.hasMember:Observation</t>
@@ -816,7 +798,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -836,7 +818,7 @@
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -849,7 +831,7 @@
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -862,7 +844,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -888,7 +870,7 @@
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -901,7 +883,7 @@
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -927,7 +909,7 @@
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -940,7 +922,7 @@
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -953,7 +935,7 @@
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E13" s="2"/>
     </row>
@@ -979,7 +961,7 @@
         <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -992,85 +974,85 @@
         <v>32</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2"/>
     </row>

--- a/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:13:01+00:00</t>
+    <t>2026-08-25T11:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:34:21+00:00</t>
+    <t>2026-08-25T11:56:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:56:50+00:00</t>
+    <t>2026-08-25T20:08:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRObservationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T20:08:46+00:00</t>
+    <t>2026-08-31T08:09:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
